--- a/output/pdf_financials_xlsx/ACX.xlsx
+++ b/output/pdf_financials_xlsx/ACX.xlsx
@@ -2372,31 +2372,31 @@
         <v>1.426</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1.898</v>
+        <v>0.001898</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.002683</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.006875</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.007223</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.002898</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.011175</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.010731</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.012792</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.03465</v>
       </c>
     </row>
     <row r="35">
@@ -2488,31 +2488,31 @@
         <v>1.426</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1.898</v>
+        <v>0.001898</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.002683</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.006875</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.007223</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.002898</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.011175</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.010731</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.012792</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.03465</v>
       </c>
     </row>
     <row r="37">
@@ -3184,31 +3184,31 @@
         <v>4.95</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0</v>
+        <v>0.020188</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.005743</v>
+        <v>0.00306</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.008566000000000001</v>
+        <v>0.001691</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.008891</v>
+        <v>0.001668</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.004336</v>
+        <v>0.001438</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.015704</v>
+        <v>0.004529</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.01657</v>
+        <v>0.005839</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.021887</v>
+        <v>0.009095000000000001</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.044036</v>
+        <v>0.009386</v>
       </c>
     </row>
     <row r="49">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">

--- a/output/pdf_financials_xlsx/ACX.xlsx
+++ b/output/pdf_financials_xlsx/ACX.xlsx
@@ -6903,10 +6903,10 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.003761</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.004219</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -6915,19 +6915,19 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>11.596</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>29.547</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>4.944</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>5.286</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -6939,16 +6939,16 @@
         <v>0</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.003553</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.001678</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.001187</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>0.001768</v>
       </c>
       <c r="R112" s="3" t="n">
         <v>0</v>
@@ -33661,7 +33661,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -49333,7 +49337,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E416" s="5" t="n">
         <v>0.003761</v>
       </c>

--- a/output/pdf_financials_xlsx/ACX.xlsx
+++ b/output/pdf_financials_xlsx/ACX.xlsx
@@ -1340,13 +1340,13 @@
         <v>4.687</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>3.255</v>
+        <v>3.947</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-5.778278</v>
+        <v>-0.003339</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.000611</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>0.010922</v>
@@ -1361,13 +1361,13 @@
         <v>0.004614</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>-0.009559</v>
+        <v>0.009559</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>0.010103</v>
+        <v>-0.010103</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>0.007637</v>
+        <v>-0.007637</v>
       </c>
     </row>
     <row r="18">
@@ -1576,13 +1576,15 @@
         <v>0.014797</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>3.77</v>
+        <v>-1.542</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>19.657</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>-35.342</v>
+        <v>10.283</v>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="3" t="n">
         <v>0.002617</v>
@@ -1591,7 +1593,7 @@
         <v>0.000229</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.004783</v>
+        <v>-0.017061</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.018247</v>
@@ -1622,10 +1624,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-0.004991</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>-0.002514</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -1640,13 +1642,13 @@
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>-6.501</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>-0.004089</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>-0.000142</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>0</v>
@@ -1747,25 +1749,25 @@
         <v>0.027634</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.014797</v>
+        <v>14.797</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3.77</v>
+        <v>-1.542</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>19.657</v>
+        <v>10.283</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-35.342</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-5.779</v>
+        <v>-0.005779</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-0.000382</v>
+        <v>8.7e-05</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.004783</v>
+        <v>-0.017061</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-0.018247</v>
@@ -1957,7 +1959,7 @@
         <v>36.435052</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-82.557143</v>
+        <v>-0.08255700000000001</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
@@ -1965,7 +1967,7 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.014068</v>
+        <v>0.050179</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>0.046787</v>
@@ -2246,13 +2248,13 @@
         <v>31.30928523714095</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-13.07543986502772</v>
+        <v>-15.85522615891379</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-800315.512465374</v>
+        <v>-462.4653739612189</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0</v>
+        <v>-159.9476439790576</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>-177.9117120052126</v>
@@ -2295,25 +2297,25 @@
         <v>12.54021773165186</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.00728220321466185</v>
+        <v>7.28220321466185</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.677904622026392</v>
+        <v>-0.6862941451365244</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>7.136711020748996</v>
+        <v>3.73336721912611</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>-96.04848353081856</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-7146.390324734746</v>
+        <v>-7.146390324734746</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>-0.2596961147557701</v>
+        <v>0.05914545021924606</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>2.974003121366437</v>
+        <v>-10.60829338357365</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>-15.17094017094017</v>
@@ -4313,31 +4315,31 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.01235</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>9.295</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>11.635</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>18.454</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.003512</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.005265</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.009271</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.00537</v>
       </c>
       <c r="N67" s="3" t="n">
         <v>0</v>
@@ -4371,31 +4373,31 @@
         <v>0.021309</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.028046</v>
+        <v>0.040396</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>21.773</v>
+        <v>31.068</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>22.236</v>
+        <v>33.871</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>35.201</v>
+        <v>53.655</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>20.198</v>
+        <v>24.188</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.012837</v>
+        <v>0.016349</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.017926</v>
+        <v>0.023191</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.023868</v>
+        <v>0.033139</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0.011308</v>
+        <v>0.016678</v>
       </c>
       <c r="N68" s="3" t="n">
         <v>0.011069</v>
@@ -4777,31 +4779,31 @@
         <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.015867</v>
+        <v>0.003517</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>4.359</v>
+        <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>13.825</v>
+        <v>2.19</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>6.152</v>
+        <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.004207</v>
+        <v>0.000695</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.001814</v>
+        <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.001432</v>
+        <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.002627</v>
+        <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
         <v>0.003182</v>
@@ -6161,25 +6163,25 @@
         <v>0.027634</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.014797</v>
+        <v>14.797</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>3.77</v>
+        <v>-1.542</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>19.657</v>
+        <v>10.283</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>-35.342</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>-5.779</v>
+        <v>-0.005779</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>-0.000382</v>
+        <v>8.7e-05</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>0.004783</v>
+        <v>-0.017061</v>
       </c>
       <c r="M99" s="3" t="n">
         <v>-0.018247</v>
@@ -6555,55 +6557,55 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>-0.004681</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>0.006297</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>-0.006731</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>-0.021857</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>27.724</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>-10.082</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>25.794</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>0.00157</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.012661</v>
+        <v>-0.008947999999999999</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.014597</v>
+        <v>0.004044</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>0.009247</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0</v>
+        <v>-0.005263</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0</v>
+        <v>-0.027113</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0</v>
+        <v>-0.012141</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0</v>
+        <v>-0.002191</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>0</v>
+        <v>0.017942</v>
       </c>
     </row>
     <row r="107">
@@ -7437,10 +7439,10 @@
         <v>0</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-3.962</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-4.434</v>
       </c>
       <c r="H121" s="3" t="n">
         <v>0</v>
@@ -30765,7 +30767,11 @@
           <t>Changes in non-cash operating working capital (note 13)</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -33269,7 +33275,11 @@
           <t>Changes in non-cash operating working capital (note 14)</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -35043,7 +35053,11 @@
           <t>Changes in non-cash operating working capital (note 15)</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -36007,7 +36021,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -36931,7 +36949,11 @@
           <t>Changes in non-cash operating w orking capital (note 14)</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -38867,7 +38889,11 @@
           <t>Changes in non-cash operating w orking capital (note 18)</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -39922,7 +39948,11 @@
           <t>Changes in non-cash operating w orking capital (note 19)</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -40298,7 +40328,11 @@
           <t>Proceeds on share issuance from bought deal public offering and insider private placement</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -44496,7 +44530,11 @@
           <t>Total deferred tax recovery</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -47185,7 +47223,11 @@
           <t>Issued on bought deal and private placement - -</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -47977,7 +48019,11 @@
           <t>Changes in non-cash operating w orking capital (note 21)</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E402" t="inlineStr">
         <is>
           <t>-</t>
@@ -51247,7 +51293,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
           <t>-</t>
@@ -51944,7 +51994,11 @@
           <t>Changes in non-cash operating w orking capital (note 20)</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E443" t="inlineStr">
         <is>
           <t>-</t>
@@ -52445,7 +52499,11 @@
           <t>Future income tax (recovery)</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
           <t>-</t>
@@ -52744,7 +52802,11 @@
           <t>Changes in non-cash operating working capital (note 14)</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
           <t>-</t>
@@ -53938,7 +54000,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E463" s="5" t="n">
         <v>-0.001893</v>
       </c>
@@ -54037,7 +54103,11 @@
           <t>Changes in non-cash operating working capital (note 13)</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E464" s="5" t="n">
         <v>-0.004681</v>
       </c>
@@ -56671,7 +56741,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
           <t>-</t>
@@ -59930,7 +60004,11 @@
           <t>Income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr"/>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E525" t="inlineStr">
         <is>
           <t>-</t>
@@ -68695,7 +68773,11 @@
           <t>Total income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D614" t="inlineStr"/>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E614" t="inlineStr">
         <is>
           <t>-</t>
@@ -68885,7 +68967,11 @@
           <t>Net loss from discontinued operations (note 10)</t>
         </is>
       </c>
-      <c r="D616" t="inlineStr"/>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E616" t="inlineStr">
         <is>
           <t>-</t>
@@ -68982,7 +69068,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D617" t="inlineStr"/>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E617" t="inlineStr">
         <is>
           <t>-</t>
@@ -69887,7 +69977,11 @@
           <t>Total income tax recovery</t>
         </is>
       </c>
-      <c r="D626" t="inlineStr"/>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E626" t="inlineStr">
         <is>
           <t>-</t>
@@ -73875,7 +73969,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D666" t="inlineStr"/>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E666" t="inlineStr">
         <is>
           <t>-</t>
@@ -77057,7 +77155,11 @@
           <t>Loss from discontinued operations (note 4)</t>
         </is>
       </c>
-      <c r="D698" t="inlineStr"/>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E698" t="inlineStr">
         <is>
           <t>-</t>
